--- a/output/full_scan/batch_seq3_2026-07-09.xlsx
+++ b/output/full_scan/batch_seq3_2026-07-09.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1290.269568919019</v>
+        <v>1280.269568919019</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>112</v>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1259.242608271529</v>
+        <v>1274.242608271529</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1005</v>
@@ -1121,7 +1121,7 @@
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>975.7250056846764</v>
+        <v>965.7250056846764</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>68</v>
@@ -1386,7 +1386,7 @@
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>899.2560219934104</v>
+        <v>889.2560219934104</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>160.5</v>
@@ -1481,21 +1481,21 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>3022</v>
+        <v>2801</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>威強電</t>
+          <t>彰銀</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>876.153145107724</v>
+        <v>875.6219472945788</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>89</v>
+        <v>24.05</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>61.02928662731235</v>
+        <v>70.76992785133268</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>37.06858327314302</v>
+        <v>61.34479444599594</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.63725874971997</v>
+        <v>0.6439816452855772</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3542649498157608</v>
+        <v>-0.0153977889473611</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>2801</v>
+        <v>2634</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>彰銀</t>
+          <t>漢翔</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>875.6219472945788</v>
+        <v>872.7434509980446</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>24.05</v>
+        <v>58</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>70.76992785133268</v>
+        <v>65.29978788719649</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>61.34479444599594</v>
+        <v>31.81295073993225</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.6439816452855772</v>
+        <v>1.37434509980446</v>
       </c>
       <c r="K21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.0153977889473611</v>
+        <v>0.8050083736298621</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>2634</v>
+        <v>2908</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>漢翔</t>
+          <t>特力</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>872.7434509980446</v>
+        <v>869.9039828533685</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>58</v>
+        <v>21.85</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>65.29978788719649</v>
+        <v>64.82806738597085</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>31.81295073993225</v>
+        <v>17.24065543759859</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.37434509980446</v>
+        <v>0.8729458263442524</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.8050083736298621</v>
+        <v>0.0459501411239101</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>2908</v>
+        <v>3034</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>特力</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>869.9039828533685</v>
+        <v>868.4846923881031</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>21.85</v>
+        <v>542</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,49 +1665,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>64.82806738597085</v>
+        <v>58.54715463097499</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>17.24065543759859</v>
+        <v>33.64048687846246</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.8729458263442524</v>
+        <v>1.027700217484978</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0459501411239101</v>
+        <v>-1.367158873666309</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3034</v>
+        <v>3022</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>威強電</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>868.4846923881031</v>
+        <v>866.153145107724</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>542</v>
+        <v>89</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,29 +1718,29 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>58.54715463097499</v>
+        <v>61.02928662731235</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>33.64048687846246</v>
+        <v>37.06858327314302</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.027700217484978</v>
+        <v>1.63725874971997</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-1.367158873666309</v>
+        <v>0.3542649498157608</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1799,21 +1799,21 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>2912</v>
+        <v>3023</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>信邦</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>844.1285816944428</v>
+        <v>855.1118144816724</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>241</v>
+        <v>326</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,49 +1824,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>65.30443690453183</v>
+        <v>52.94484465583722</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>20.99512892323743</v>
+        <v>18.43596642224752</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.8636820244649274</v>
+        <v>0.8281557277831393</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.834183632785356</v>
+        <v>-0.7820885997675893</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>2466</v>
+        <v>2912</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>冠西電</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>843.3586251706981</v>
+        <v>844.1285816944428</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>98.5</v>
+        <v>241</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,29 +1877,29 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>89.13225652300333</v>
+        <v>65.30443690453183</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>50.29864040655482</v>
+        <v>20.99512892323743</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5337382475575092</v>
+        <v>0.8636820244649274</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>4.268355285617312</v>
+        <v>1.834183632785356</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1958,21 +1958,21 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>3023</v>
+        <v>2889</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>國票金</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>840.1118144816724</v>
+        <v>831.7938103664732</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>326</v>
+        <v>15.8</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>52.94484465583722</v>
+        <v>73.04153309328504</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>18.43596642224752</v>
+        <v>18.84565939469172</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8281557277831393</v>
+        <v>2.779381036647313</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.7820885997675893</v>
+        <v>0.08468460153072729</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>2889</v>
+        <v>2886</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>國票金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>831.7938103664732</v>
+        <v>831.1172192090519</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>15.8</v>
+        <v>46.7</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>73.04153309328504</v>
+        <v>67.9080808546468</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>18.84565939469172</v>
+        <v>47.13618712050753</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2.779381036647313</v>
+        <v>0.318308249167882</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.08468460153072729</v>
+        <v>-0.0541758274661323</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>2886</v>
+        <v>2897</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>王道銀行</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>831.1172192090519</v>
+        <v>829.348445729201</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>46.7</v>
+        <v>10.55</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,25 +2089,25 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>67.9080808546468</v>
+        <v>57.17070420309621</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>47.13618712050753</v>
+        <v>31.875219178941</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.318308249167882</v>
+        <v>0.9127721139952208</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.0541758274661323</v>
+        <v>-0.0102254666375235</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2117,21 +2117,21 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>2897</v>
+        <v>2466</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>王道銀行</t>
+          <t>冠西電</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>829.348445729201</v>
+        <v>823.3586251706981</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>10.55</v>
+        <v>98.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,29 +2142,29 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>57.17070420309621</v>
+        <v>89.13225652300333</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>31.875219178941</v>
+        <v>50.29864040655482</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.9127721139952208</v>
+        <v>0.5337382475575092</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.0102254666375235</v>
+        <v>4.268355285617312</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -4078,21 +4078,21 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>2851</v>
+        <v>2493</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>中再保</t>
+          <t>揚博</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>656.3758089175022</v>
+        <v>668.6860404350898</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>37.85</v>
+        <v>274</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,49 +4103,49 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>53.43316085030995</v>
+        <v>58.33303493736793</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>27.53842432629391</v>
+        <v>47.95291889255274</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4731676393418583</v>
+        <v>0.939109304055768</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1105575978791969</v>
+        <v>-4.89586713107596</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>2528</v>
+        <v>2851</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>皇普</t>
+          <t>中再保</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>655.2668118935579</v>
+        <v>656.3758089175022</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>22.45</v>
+        <v>37.85</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,49 +4156,49 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>53.81936031508304</v>
+        <v>53.43316085030995</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>24.2513793087535</v>
+        <v>27.53842432629391</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.153102800926545</v>
+        <v>0.4731676393418583</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M70" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.1053607248585406</v>
+        <v>-0.1105575978791969</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>2542</v>
+        <v>2528</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>皇普</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>654.1159605725387</v>
+        <v>655.2668118935579</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>43.6</v>
+        <v>22.45</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,49 +4209,49 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>51.78001136838006</v>
+        <v>53.81936031508304</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>21.59973985166726</v>
+        <v>24.2513793087535</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.2675195273419964</v>
+        <v>1.153102800926545</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.06931788042769819</v>
+        <v>0.1053607248585406</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>2493</v>
+        <v>2542</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>揚博</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>653.6860404350898</v>
+        <v>654.1159605725387</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>274</v>
+        <v>43.6</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,49 +4262,49 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>58.33303493736793</v>
+        <v>51.78001136838006</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>47.95291889255274</v>
+        <v>21.59973985166726</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.939109304055768</v>
+        <v>0.2675195273419964</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M72" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-4.89586713107596</v>
+        <v>-0.06931788042769819</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>3088</v>
+        <v>2478</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>艾訊</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>646.0203305112108</v>
+        <v>651.2598587596734</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,49 +4315,49 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>54.41931637430952</v>
+        <v>43.91648333367947</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>18.63688654174847</v>
+        <v>45.61271217937819</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.7839048579862525</v>
+        <v>0.7729715436955409</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M73" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.2685468948682938</v>
+        <v>-9.678822417978331</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>3024</v>
+        <v>3088</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>憶聲</t>
+          <t>艾訊</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>644.6835415692826</v>
+        <v>646.0203305112108</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>12.4</v>
+        <v>144</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>44.32182522935857</v>
+        <v>54.41931637430952</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>33.37426163765993</v>
+        <v>18.63688654174847</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.958652661255145</v>
+        <v>0.7839048579862525</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0975524599821582</v>
+        <v>-0.2685468948682938</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>2640</v>
+        <v>3024</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>憶聲</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>642.7343763819517</v>
+        <v>644.6835415692826</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>158</v>
+        <v>12.4</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>50.68392183012655</v>
+        <v>44.32182522935857</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>19.24665102594777</v>
+        <v>33.37426163765993</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.890821473964619</v>
+        <v>1.958652661255145</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.9384022263767148</v>
+        <v>0.0975524599821582</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>2852</v>
+        <v>2640</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>第一保</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>642.165709149744</v>
+        <v>642.7343763819517</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>26.8</v>
+        <v>158</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>49.81856643830618</v>
+        <v>50.68392183012655</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>19.88726556830952</v>
+        <v>19.24665102594777</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3094959265432373</v>
+        <v>1.890821473964619</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0081341657863659</v>
+        <v>0.9384022263767148</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>2883</v>
+        <v>2852</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>第一保</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>641.3468872665617</v>
+        <v>642.165709149744</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>30.05</v>
+        <v>26.8</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>61.46736643659451</v>
+        <v>49.81856643830618</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>40.06732015149876</v>
+        <v>19.88726556830952</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.45069560169797</v>
+        <v>0.3094959265432373</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.1835102222178701</v>
+        <v>0.0081341657863659</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>3094</v>
+        <v>2883</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>聯傑</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>638.2222222359422</v>
+        <v>641.3468872665617</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>40.35</v>
+        <v>30.05</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>54.58552617204919</v>
+        <v>61.46736643659451</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>29.41735891291653</v>
+        <v>40.06732015149876</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5049136453949247</v>
+        <v>0.45069560169797</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.1595954362069749</v>
+        <v>-0.1835102222178701</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>2762</v>
+        <v>3094</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>世界健身-KY</t>
+          <t>聯傑</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>636.3546931655547</v>
+        <v>638.2222222359422</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>40.35</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>46.54209396467091</v>
+        <v>54.58552617204919</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>22.80884756063642</v>
+        <v>29.41735891291653</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.9914255248309232</v>
+        <v>0.5049136453949247</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.3867505547554648</v>
+        <v>-0.1595954362069749</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>2478</v>
+        <v>2762</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>大毅</t>
+          <t>世界健身-KY</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>636.2598587596734</v>
+        <v>636.3546931655547</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>174</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,29 +4686,29 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>43.91648333367947</v>
+        <v>46.54209396467091</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45.61271217937819</v>
+        <v>22.80884756063642</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7729715436955409</v>
+        <v>0.9914255248309232</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-9.678822417978331</v>
+        <v>-0.3867505547554648</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -4873,21 +4873,21 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>3047</v>
+        <v>3014</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>訊舟</t>
+          <t>聯陽</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>623.1143285282922</v>
+        <v>628.7386413622282</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>16.65</v>
+        <v>139.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,49 +4898,49 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>56.97257600804862</v>
+        <v>37.44528515161971</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>20.1744927704032</v>
+        <v>30.88708799356924</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.106844933951962</v>
+        <v>1.245988587187753</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.1026495381353902</v>
+        <v>-2.341881602692336</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>3033</v>
+        <v>3047</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>威健</t>
+          <t>訊舟</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>622.7799113430248</v>
+        <v>623.1143285282922</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>49.6</v>
+        <v>16.65</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>52.67249449737216</v>
+        <v>56.97257600804862</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>28.74947908522636</v>
+        <v>20.1744927704032</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4991261024351685</v>
+        <v>1.106844933951962</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.2233057122313316</v>
+        <v>0.1026495381353902</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>3014</v>
+        <v>3033</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>聯陽</t>
+          <t>威健</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>613.7386413622282</v>
+        <v>612.7799113430248</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>139.5</v>
+        <v>49.6</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,29 +5004,29 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>37.44528515161971</v>
+        <v>52.67249449737216</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>30.88708799356924</v>
+        <v>28.74947908522636</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.245988587187753</v>
+        <v>0.4991261024351685</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-2.341881602692336</v>
+        <v>-0.2233057122313316</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -5403,21 +5403,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>3015</v>
+        <v>2636</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>全漢</t>
+          <t>台驊控股</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>581.6645656738698</v>
+        <v>578.6841630655416</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>64.2</v>
+        <v>70.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>52.83518244415001</v>
+        <v>53.91986886833792</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>27.63378324309689</v>
+        <v>16.45836884107185</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4412888061169487</v>
+        <v>0.6698835545367614</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0011379866859728</v>
+        <v>-0.0030261411646108</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>3035</v>
+        <v>3095</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>及成</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>578.93696781055</v>
+        <v>577.6675847215466</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>216</v>
+        <v>38.15</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>54.03594690965624</v>
+        <v>41.71805266236701</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>18.63480863910756</v>
+        <v>15.55358308158649</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.6869139707892337</v>
+        <v>0.997648138587736</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-1.100306872291286</v>
+        <v>0.0255431465855772</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>2636</v>
+        <v>3052</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>台驊控股</t>
+          <t>夆典</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>578.6841630655416</v>
+        <v>574.3826197521344</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>70.5</v>
+        <v>10.9</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>53.91986886833792</v>
+        <v>55.11889506485975</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.45836884107185</v>
+        <v>16.16238926864554</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6698835545367614</v>
+        <v>0.459610163749915</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>2</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0030261411646108</v>
+        <v>0.0188698884035225</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>3095</v>
+        <v>3046</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>及成</t>
+          <t>建碁</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>577.6675847215466</v>
+        <v>573.6559006450593</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>38.15</v>
+        <v>55.6</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>41.71805266236701</v>
+        <v>53.29952786187116</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>15.55358308158649</v>
+        <v>21.15051914044751</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.997648138587736</v>
+        <v>1.01154735433469</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0255431465855772</v>
+        <v>0.2023145055036529</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>3052</v>
+        <v>3114</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>夆典</t>
+          <t>好德</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>574.3826197521344</v>
+        <v>571.8456017874765</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>10.9</v>
+        <v>40</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>55.11889506485975</v>
+        <v>44.86736586054044</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>16.16238926864554</v>
+        <v>42.06812601186997</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.459610163749915</v>
+        <v>0.5821221343388426</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0188698884035225</v>
+        <v>-1.684221199185625</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>3046</v>
+        <v>2706</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>建碁</t>
+          <t>第一店</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>573.6559006450593</v>
+        <v>569.2072138784013</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>55.6</v>
+        <v>12.55</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>53.29952786187116</v>
+        <v>57.76774385564872</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>21.15051914044751</v>
+        <v>16.26489604311163</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.01154735433469</v>
+        <v>0.4159034736005049</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.2023145055036529</v>
+        <v>0.004928892669047</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>3114</v>
+        <v>3035</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>好德</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>571.8456017874765</v>
+        <v>568.93696781055</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>40</v>
+        <v>216</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>44.86736586054044</v>
+        <v>54.03594690965624</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>42.06812601186997</v>
+        <v>18.63480863910756</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5821221343388426</v>
+        <v>0.6869139707892337</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>3</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.684221199185625</v>
+        <v>-1.100306872291286</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>2706</v>
+        <v>2472</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>第一店</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>569.2072138784013</v>
+        <v>568.7588766375127</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>12.55</v>
+        <v>376</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,49 +5799,49 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>57.76774385564872</v>
+        <v>51.14012321606164</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>16.26489604311163</v>
+        <v>36.34353459161058</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.4159034736005049</v>
+        <v>0.6142161099556175</v>
       </c>
       <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M101" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.004928892669047</v>
+        <v>-9.148355780322742</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>2472</v>
+        <v>3067</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>全域</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>568.7588766375127</v>
+        <v>566.5479367826589</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>376</v>
+        <v>18.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,49 +5852,49 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>51.14012321606164</v>
+        <v>51.72684318383804</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>36.34353459161058</v>
+        <v>8.760093608774589</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6142161099556175</v>
+        <v>0.556653399760639</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-9.148355780322742</v>
+        <v>0.214634893845478</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>3067</v>
+        <v>2911</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>全域</t>
+          <t>麗嬰房</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>566.5479367826589</v>
+        <v>564.0899039614578</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>18.5</v>
+        <v>7.84</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>51.72684318383804</v>
+        <v>53.39146344107689</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>8.760093608774589</v>
+        <v>19.72819143099765</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.556653399760639</v>
+        <v>0.5296081798595479</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.214634893845478</v>
+        <v>0.0021581216590098</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>2911</v>
+        <v>3015</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>麗嬰房</t>
+          <t>全漢</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>564.0899039614578</v>
+        <v>561.6645656738698</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>7.84</v>
+        <v>64.2</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>53.39146344107689</v>
+        <v>52.83518244415001</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>19.72819143099765</v>
+        <v>27.63378324309689</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5296081798595479</v>
+        <v>0.4412888061169487</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,11 +5976,11 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0021581216590098</v>
+        <v>0.0011379866859728</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>3073</v>
+        <v>3045</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>天方能源</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>499.2337368577561</v>
+        <v>499.5105669229774</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>22</v>
+        <v>108.5</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>50.7709844566271</v>
+        <v>28.61825215344104</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>20.47660706899832</v>
+        <v>24.1905696067152</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.6276859944218266</v>
+        <v>3.35105669229774</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.0916149920180276</v>
+        <v>-1.125708078864336</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>3056</v>
+        <v>3073</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>富華新</t>
+          <t>天方能源</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>496.569664670454</v>
+        <v>499.2337368577561</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>14.85</v>
+        <v>22</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>54.72861387941937</v>
+        <v>50.7709844566271</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>16.80393407123563</v>
+        <v>20.47660706899832</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.5263924075930559</v>
+        <v>0.6276859944218266</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0268880562294273</v>
+        <v>0.0916149920180276</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>2608</v>
+        <v>2449</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>嘉里大榮</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>495.8506033487794</v>
+        <v>497.2589805261128</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>29.45</v>
+        <v>308.5</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,49 +7230,49 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>54.13420944703902</v>
+        <v>47.84655340429072</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>19.4644188259638</v>
+        <v>17.52598431710268</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.5327558711538301</v>
+        <v>0.5395764240340419</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L128" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M128" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.0715435705266575</v>
+        <v>-1.672184535486778</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>2615</v>
+        <v>3056</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>富華新</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>494.3037441301998</v>
+        <v>496.569664670454</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>14.85</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>50.86622544126677</v>
+        <v>54.72861387941937</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>16.0731958927454</v>
+        <v>16.80393407123563</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>1.072841082822381</v>
+        <v>0.5263924075930559</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0230427589537847</v>
+        <v>-0.0268880562294273</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>2543</v>
+        <v>2608</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>皇昌</t>
+          <t>嘉里大榮</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>490.9714112813516</v>
+        <v>495.8506033487794</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>38.8</v>
+        <v>29.45</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,16 +7336,16 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>37.13835184398473</v>
+        <v>54.13420944703902</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>21.48624933012236</v>
+        <v>19.4644188259638</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.5328603015593036</v>
+        <v>0.5327558711538301</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.07583758812724629</v>
+        <v>0.0715435705266575</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>3045</v>
+        <v>2615</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>489.5105669229774</v>
+        <v>494.3037441301998</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>108.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>28.61825215344104</v>
+        <v>50.86622544126677</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>24.1905696067152</v>
+        <v>16.0731958927454</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>3.35105669229774</v>
+        <v>1.072841082822381</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-1.125708078864336</v>
+        <v>-0.0230427589537847</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>2617</v>
+        <v>2543</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>台航</t>
+          <t>皇昌</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>488.2451486821784</v>
+        <v>490.9714112813516</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>30.5</v>
+        <v>38.8</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,16 +7442,16 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>59.33309079760946</v>
+        <v>37.13835184398473</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>13.24332147462513</v>
+        <v>21.48624933012236</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.7360449314441664</v>
+        <v>0.5328603015593036</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.0722253951957431</v>
+        <v>-0.07583758812724629</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>2460</v>
+        <v>2617</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>建通</t>
+          <t>台航</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>486.7437696106047</v>
+        <v>488.2451486821784</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>34.3</v>
+        <v>30.5</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,16 +7495,16 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>46.66753326083748</v>
+        <v>59.33309079760946</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>22.75729851808959</v>
+        <v>13.24332147462513</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>1.021953321395523</v>
+        <v>0.7360449314441664</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="2" t="n">
         <v>0</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.2085913455684558</v>
+        <v>0.0722253951957431</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>3029</v>
+        <v>2460</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>建通</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>486.5362303897544</v>
+        <v>486.7437696106047</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>103</v>
+        <v>34.3</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,16 +7548,16 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>54.22472188978693</v>
+        <v>46.66753326083748</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>12.74087102319846</v>
+        <v>22.75729851808959</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.7904210408516731</v>
+        <v>1.021953321395523</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L134" s="2" t="n">
         <v>0</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>0.3331790543751955</v>
+        <v>-0.2085913455684558</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>3031</v>
+        <v>2471</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>佰鴻</t>
+          <t>資通</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>485.6044551577343</v>
+        <v>483.012503951619</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>30.85</v>
+        <v>53.2</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,13 +7601,13 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>48.42852373914201</v>
+        <v>51.51269854591602</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>24.70737000655168</v>
+        <v>11.9493841565906</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.3715386603295649</v>
+        <v>0.4179962674339422</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>0</v>
@@ -7619,31 +7619,31 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>0.0546674776978376</v>
+        <v>-0.0016340680262111</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>2471</v>
+        <v>2731</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>資通</t>
+          <t>雄獅</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>483.012503951619</v>
+        <v>476.6071263236449</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>53.2</v>
+        <v>145.5</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,13 +7654,13 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>51.51269854591602</v>
+        <v>30.88348934736115</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>11.9493841565906</v>
+        <v>23.33322271680851</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.4179962674339422</v>
+        <v>0.9235818372441584</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>0</v>
@@ -7672,31 +7672,31 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>-0.0016340680262111</v>
+        <v>-0.0951940029337965</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>2449</v>
+        <v>3029</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>482.2589805261128</v>
+        <v>476.5362303897544</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>308.5</v>
+        <v>103</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,49 +7707,49 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>47.84655340429072</v>
+        <v>54.22472188978693</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>17.52598431710268</v>
+        <v>12.74087102319846</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.5395764240340419</v>
+        <v>0.7904210408516731</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M137" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-1.672184535486778</v>
+        <v>0.3331790543751955</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>2731</v>
+        <v>3031</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>雄獅</t>
+          <t>佰鴻</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>476.6071263236449</v>
+        <v>475.6044551577343</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>145.5</v>
+        <v>30.85</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,13 +7760,13 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>30.88348934736115</v>
+        <v>48.42852373914201</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>23.33322271680851</v>
+        <v>24.70737000655168</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.9235818372441584</v>
+        <v>0.3715386603295649</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>0</v>
@@ -7778,11 +7778,11 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.0951940029337965</v>
+        <v>0.0546674776978376</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -8106,21 +8106,21 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>3002</v>
+        <v>2464</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>歐格</t>
+          <t>盟立</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>457.2449589827172</v>
+        <v>457.6688788732395</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>20.45</v>
+        <v>161.5</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>48.96783905627235</v>
+        <v>49.22537311513194</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>35.60455543350986</v>
+        <v>16.25449781630469</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.2916001953823394</v>
+        <v>0.48381401441041</v>
       </c>
       <c r="K145" s="2" t="n">
         <v>0</v>
@@ -8149,31 +8149,31 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.1917893926327997</v>
+        <v>-2.701694674852127</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>3128</v>
+        <v>3002</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>昇銳</t>
+          <t>歐格</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>456.58954803692</v>
+        <v>457.2449589827172</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>24.2</v>
+        <v>20.45</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8184,13 +8184,13 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>48.5214880600634</v>
+        <v>48.96783905627235</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>17.52221059745274</v>
+        <v>35.60455543350986</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.3960798534820859</v>
+        <v>0.2916001953823394</v>
       </c>
       <c r="K146" s="2" t="n">
         <v>0</v>
@@ -8202,31 +8202,31 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-0.0241880218863314</v>
+        <v>-0.1917893926327997</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>2702</v>
+        <v>3128</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>華園</t>
+          <t>昇銳</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>451.9055513346614</v>
+        <v>456.58954803692</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>13.25</v>
+        <v>24.2</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -8237,16 +8237,16 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>54.36342036906096</v>
+        <v>48.5214880600634</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>15.5714975980245</v>
+        <v>17.52221059745274</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.6634294194925323</v>
+        <v>0.3960798534820859</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L147" s="2" t="n">
         <v>0</v>
@@ -8255,31 +8255,31 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>0.0943274146027184</v>
+        <v>-0.0241880218863314</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, stronger_than_market, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>2910</v>
+        <v>2702</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>統領</t>
+          <t>華園</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v/>
       </c>
       <c r="D148" s="2" t="n">
-        <v>447.8789713603437</v>
+        <v>451.9055513346614</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>22.35</v>
+        <v>13.25</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8290,13 +8290,13 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>51.56655281282952</v>
+        <v>54.36342036906096</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>18.80213839323954</v>
+        <v>15.5714975980245</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>4.574008443817027</v>
+        <v>0.6634294194925323</v>
       </c>
       <c r="K148" s="2" t="n">
         <v>1</v>
@@ -8308,31 +8308,31 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>0.2168277833229515</v>
+        <v>0.0943274146027184</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>3036</v>
+        <v>2910</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>統領</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v/>
       </c>
       <c r="D149" s="2" t="n">
-        <v>446.7852680239446</v>
+        <v>447.8789713603437</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>211.5</v>
+        <v>22.35</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -8343,13 +8343,13 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>35.98144615712485</v>
+        <v>51.56655281282952</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>32.83033417778038</v>
+        <v>18.80213839323954</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>0.3711452412630785</v>
+        <v>4.574008443817027</v>
       </c>
       <c r="K149" s="2" t="n">
         <v>1</v>
@@ -8361,31 +8361,31 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>0.4634909546672094</v>
+        <v>0.2168277833229515</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>2727</v>
+        <v>3036</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>王品</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v/>
       </c>
       <c r="D150" s="2" t="n">
-        <v>444.1408799967263</v>
+        <v>446.7852680239446</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>240.5</v>
+        <v>211.5</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -8396,16 +8396,16 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>43.53992900790104</v>
+        <v>35.98144615712485</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>29.89134816407147</v>
+        <v>32.83033417778038</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>1.269810926407299</v>
+        <v>0.3711452412630785</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L150" s="2" t="n">
         <v>0</v>
@@ -8414,31 +8414,31 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>-1.187851522410465</v>
+        <v>0.4634909546672094</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>2464</v>
+        <v>2727</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>盟立</t>
+          <t>王品</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>442.6688788732395</v>
+        <v>444.1408799967263</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>161.5</v>
+        <v>240.5</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -8449,13 +8449,13 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>49.22537311513194</v>
+        <v>43.53992900790104</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>16.25449781630469</v>
+        <v>29.89134816407147</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.48381401441041</v>
+        <v>1.269810926407299</v>
       </c>
       <c r="K151" s="2" t="n">
         <v>0</v>
@@ -8467,11 +8467,11 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>-2.701694674852127</v>
+        <v>-1.187851522410465</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -8636,21 +8636,21 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>2498</v>
+        <v>2539</v>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>宏達電</t>
+          <t>櫻花建</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v/>
       </c>
       <c r="D155" s="2" t="n">
-        <v>427.1581376234904</v>
+        <v>425.8970073757017</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>45.15</v>
+        <v>39.3</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -8661,13 +8661,13 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>51.17033540218756</v>
+        <v>52.42967740170658</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>18.66847604559499</v>
+        <v>22.41558865919445</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.5317562068798675</v>
+        <v>0.3438768134343579</v>
       </c>
       <c r="K155" s="2" t="n">
         <v>1</v>
@@ -8679,31 +8679,31 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>-0.0975821352131535</v>
+        <v>0.0851001238442548</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>2539</v>
+        <v>2450</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>櫻花建</t>
+          <t>神腦</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v/>
       </c>
       <c r="D156" s="2" t="n">
-        <v>425.8970073757017</v>
+        <v>425.6735293310371</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>39.3</v>
+        <v>28.75</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -8714,13 +8714,13 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>52.42967740170658</v>
+        <v>38.41972199390736</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>22.41558865919445</v>
+        <v>20.85205531340522</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.3438768134343579</v>
+        <v>0.5704255538604479</v>
       </c>
       <c r="K156" s="2" t="n">
         <v>1</v>
@@ -8732,31 +8732,31 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>0.0851001238442548</v>
+        <v>-0.038848360096077</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>2450</v>
+        <v>2613</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>神腦</t>
+          <t>中櫃</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v/>
       </c>
       <c r="D157" s="2" t="n">
-        <v>425.6735293310371</v>
+        <v>423.3549046143612</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>28.75</v>
+        <v>21.75</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -8767,16 +8767,16 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>38.41972199390736</v>
+        <v>47.49161170352213</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>20.85205531340522</v>
+        <v>10.72513098747152</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0.5704255538604479</v>
+        <v>0.5247132882845551</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L157" s="2" t="n">
         <v>0</v>
@@ -8785,31 +8785,31 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>-0.038848360096077</v>
+        <v>0.0304202108609333</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>2613</v>
+        <v>3008</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>中櫃</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v/>
       </c>
       <c r="D158" s="2" t="n">
-        <v>423.3549046143612</v>
+        <v>420.7704641946521</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>21.75</v>
+        <v>3950</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>47.49161170352213</v>
+        <v>44.06805789959837</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>10.72513098747152</v>
+        <v>25.96659461481231</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>0.5247132882845551</v>
+        <v>0.5703271937391633</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L158" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M158" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>0.0304202108609333</v>
+        <v>-147.155159101782</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>3008</v>
+        <v>2505</v>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>國揚</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v/>
       </c>
       <c r="D159" s="2" t="n">
-        <v>420.7704641946521</v>
+        <v>419.3412947907951</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>3950</v>
+        <v>17.95</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -8873,49 +8873,49 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>44.06805789959837</v>
+        <v>45.29814058016053</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>25.96659461481231</v>
+        <v>21.29556085267859</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0.5703271937391633</v>
+        <v>0.342070172501965</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L159" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>-147.155159101782</v>
+        <v>-0.060286803198436</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>2505</v>
+        <v>2498</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>國揚</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v/>
       </c>
       <c r="D160" s="2" t="n">
-        <v>419.3412947907951</v>
+        <v>417.1581376234904</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>17.95</v>
+        <v>45.15</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -8926,13 +8926,13 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>45.29814058016053</v>
+        <v>51.17033540218756</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>21.29556085267859</v>
+        <v>18.66847604559499</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>0.342070172501965</v>
+        <v>0.5317562068798675</v>
       </c>
       <c r="K160" s="2" t="n">
         <v>1</v>
@@ -8944,11 +8944,11 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>-0.060286803198436</v>
+        <v>-0.0975821352131535</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
@@ -9431,21 +9431,21 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>2524</v>
+        <v>3042</v>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>京城</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v/>
       </c>
       <c r="D170" s="2" t="n">
-        <v>396.6464006811693</v>
+        <v>398.124546753761</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>35.5</v>
+        <v>200</v>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
@@ -9456,13 +9456,13 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>47.01999511191939</v>
+        <v>48.34246612213894</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>14.64098820439675</v>
+        <v>22.78123007603793</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>0.2610851526977383</v>
+        <v>0.4152090765621014</v>
       </c>
       <c r="K170" s="2" t="n">
         <v>1</v>
@@ -9474,31 +9474,31 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.1542353393167715</v>
+        <v>-1.572792396216629</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>3093</v>
+        <v>2524</v>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>港建*</t>
+          <t>京城</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v/>
       </c>
       <c r="D171" s="2" t="n">
-        <v>396.2157381766438</v>
+        <v>396.6464006811693</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>56.4</v>
+        <v>35.5</v>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
@@ -9509,16 +9509,16 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>37.3056981160185</v>
+        <v>47.01999511191939</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>31.67192146912457</v>
+        <v>14.64098820439675</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>0.4601622573060686</v>
+        <v>0.2610851526977383</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L171" s="2" t="n">
         <v>0</v>
@@ -9527,31 +9527,31 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>-1.863834955610947</v>
+        <v>-0.1542353393167715</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>2467</v>
+        <v>3093</v>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>港建*</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v/>
       </c>
       <c r="D172" s="2" t="n">
-        <v>393.8753185603939</v>
+        <v>396.2157381766438</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>556</v>
+        <v>56.4</v>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
@@ -9562,13 +9562,13 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>44.52971900377984</v>
+        <v>37.3056981160185</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>12.31636488684985</v>
+        <v>31.67192146912457</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0.974189682903188</v>
+        <v>0.4601622573060686</v>
       </c>
       <c r="K172" s="2" t="n">
         <v>0</v>
@@ -9580,31 +9580,31 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>-4.43151221620448</v>
+        <v>-1.863834955610947</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>2722</v>
+        <v>2467</v>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>夏都</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v/>
       </c>
       <c r="D173" s="2" t="n">
-        <v>392.9766700559143</v>
+        <v>393.8753185603939</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>22.7</v>
+        <v>556</v>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
@@ -9615,16 +9615,16 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>45.19474786816313</v>
+        <v>44.52971900377984</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>22.75342751125807</v>
+        <v>12.31636488684985</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0.29448507007922</v>
+        <v>0.974189682903188</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L173" s="2" t="n">
         <v>0</v>
@@ -9633,31 +9633,31 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>-0.0320723671612332</v>
+        <v>-4.43151221620448</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>3105</v>
+        <v>2722</v>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>夏都</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v/>
       </c>
       <c r="D174" s="2" t="n">
-        <v>383.9432198906452</v>
+        <v>392.9766700559143</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>406</v>
+        <v>22.7</v>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
@@ -9668,49 +9668,49 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>36.82846146361322</v>
+        <v>45.19474786816313</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>11.93563335776272</v>
+        <v>22.75342751125807</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>0.5467009411087379</v>
+        <v>0.29448507007922</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L174" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M174" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-5.315555370480357</v>
+        <v>-0.0320723671612332</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>3042</v>
+        <v>3016</v>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>嘉晶</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v/>
       </c>
       <c r="D175" s="2" t="n">
-        <v>383.124546753761</v>
+        <v>387.6371498880827</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>200</v>
+        <v>121.5</v>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
@@ -9721,16 +9721,16 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>48.34246612213894</v>
+        <v>49.16219760044645</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>22.78123007603793</v>
+        <v>22.26011244093566</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>0.4152090765621014</v>
+        <v>0.6238218777292066</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L175" s="2" t="n">
         <v>0</v>
@@ -9739,7 +9739,7 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>-1.572792396216629</v>
+        <v>-1.975340501080123</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -9749,21 +9749,21 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>3050</v>
+        <v>3105</v>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>鈺德</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v/>
       </c>
       <c r="D176" s="2" t="n">
-        <v>378.5066114406138</v>
+        <v>383.9432198906452</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>12.45</v>
+        <v>406</v>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
@@ -9774,49 +9774,49 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>46.69982984471375</v>
+        <v>36.82846146361322</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>11.6062076777057</v>
+        <v>11.93563335776272</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>0.3477017482333847</v>
+        <v>0.5467009411087379</v>
       </c>
       <c r="K176" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L176" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M176" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>-0.0311808671556081</v>
+        <v>-5.315555370480357</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>2461</v>
+        <v>3050</v>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>光群雷</t>
+          <t>鈺德</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v/>
       </c>
       <c r="D177" s="2" t="n">
-        <v>374.7296703461897</v>
+        <v>378.5066114406138</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>17.3</v>
+        <v>12.45</v>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
@@ -9827,13 +9827,13 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>45.60492099387079</v>
+        <v>46.69982984471375</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>20.55460080847068</v>
+        <v>11.6062076777057</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>0.4574489393233838</v>
+        <v>0.3477017482333847</v>
       </c>
       <c r="K177" s="2" t="n">
         <v>0</v>
@@ -9845,31 +9845,31 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>-0.07796714526721869</v>
+        <v>-0.0311808671556081</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>2904</v>
+        <v>2461</v>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>匯僑</t>
+          <t>光群雷</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v/>
       </c>
       <c r="D178" s="2" t="n">
-        <v>372.7379215072045</v>
+        <v>374.7296703461897</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>14</v>
+        <v>17.3</v>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
@@ -9880,13 +9880,13 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>41.26191858128449</v>
+        <v>45.60492099387079</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>12.11082106648074</v>
+        <v>20.55460080847068</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>0.2527938056216133</v>
+        <v>0.4574489393233838</v>
       </c>
       <c r="K178" s="2" t="n">
         <v>0</v>
@@ -9898,31 +9898,31 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>0.0206579962687713</v>
+        <v>-0.07796714526721869</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>3016</v>
+        <v>2904</v>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>嘉晶</t>
+          <t>匯僑</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v/>
       </c>
       <c r="D179" s="2" t="n">
-        <v>372.6371498880827</v>
+        <v>372.7379215072045</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>121.5</v>
+        <v>14</v>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
@@ -9933,13 +9933,13 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>49.16219760044645</v>
+        <v>41.26191858128449</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>22.26011244093566</v>
+        <v>12.11082106648074</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>0.6238218777292066</v>
+        <v>0.2527938056216133</v>
       </c>
       <c r="K179" s="2" t="n">
         <v>0</v>
@@ -9951,11 +9951,11 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>-1.975340501080123</v>
+        <v>0.0206579962687713</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -10438,21 +10438,21 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>2485</v>
+        <v>2723</v>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>兆赫</t>
+          <t>美食-KY</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>352.4814518160049</v>
+        <v>347.9960799195127</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>49.9</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
@@ -10463,16 +10463,16 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>32.95641583628328</v>
+        <v>52.50839525449627</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>27.7511057650897</v>
+        <v>25.08484410939062</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>0.5159660697903209</v>
+        <v>0.3556796744838565</v>
       </c>
       <c r="K189" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L189" s="2" t="n">
         <v>0</v>
@@ -10481,31 +10481,31 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>-0.3754997355572058</v>
+        <v>-0.1194650832449235</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>2723</v>
+        <v>3040</v>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>美食-KY</t>
+          <t>遠見</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
         <v/>
       </c>
       <c r="D190" s="2" t="n">
-        <v>347.9960799195127</v>
+        <v>345.044208047035</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>37.5</v>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
@@ -10516,16 +10516,16 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>52.50839525449627</v>
+        <v>42.38020962164538</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>25.08484410939062</v>
+        <v>11.56970464282783</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>0.3556796744838565</v>
+        <v>0.0670674924700019</v>
       </c>
       <c r="K190" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L190" s="2" t="n">
         <v>0</v>
@@ -10534,31 +10534,31 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-0.1194650832449235</v>
+        <v>0.106276496237769</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>3040</v>
+        <v>2468</v>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>遠見</t>
+          <t>華經</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
         <v/>
       </c>
       <c r="D191" s="2" t="n">
-        <v>345.044208047035</v>
+        <v>344.5719821670326</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>37.5</v>
+        <v>36.6</v>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
@@ -10569,16 +10569,16 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>42.38020962164538</v>
+        <v>47.86817202421354</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>11.56970464282783</v>
+        <v>20.96230977418855</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>0.0670674924700019</v>
+        <v>0.2656539853445514</v>
       </c>
       <c r="K191" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L191" s="2" t="n">
         <v>0</v>
@@ -10587,31 +10587,31 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>0.106276496237769</v>
+        <v>-0.0570700042948114</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>2468</v>
+        <v>2454</v>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>華經</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>344.5719821670326</v>
+        <v>344.2209588312278</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>36.6</v>
+        <v>3925</v>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
@@ -10622,13 +10622,13 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>47.86817202421354</v>
+        <v>44.68365245488434</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>20.96230977418855</v>
+        <v>26.01246022183453</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>0.2656539853445514</v>
+        <v>0.6078396423261001</v>
       </c>
       <c r="K192" s="2" t="n">
         <v>0</v>
@@ -10640,31 +10640,31 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-0.0570700042948114</v>
+        <v>-73.32301198108311</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>2454</v>
+        <v>2616</v>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>山隆</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
         <v/>
       </c>
       <c r="D193" s="2" t="n">
-        <v>344.2209588312278</v>
+        <v>343.4896114113754</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>3925</v>
+        <v>13.65</v>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
@@ -10675,13 +10675,13 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>44.68365245488434</v>
+        <v>49.94882128177537</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>26.01246022183453</v>
+        <v>13.47230405322124</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>0.6078396423261001</v>
+        <v>0.4720267441872952</v>
       </c>
       <c r="K193" s="2" t="n">
         <v>0</v>
@@ -10693,31 +10693,31 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>-73.32301198108311</v>
+        <v>0.0349936220506823</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>2616</v>
+        <v>2485</v>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>山隆</t>
+          <t>兆赫</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
         <v/>
       </c>
       <c r="D194" s="2" t="n">
-        <v>343.4896114113754</v>
+        <v>342.4814518160049</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>13.65</v>
+        <v>49.9</v>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
@@ -10728,13 +10728,13 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>49.94882128177537</v>
+        <v>32.95641583628328</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>13.47230405322124</v>
+        <v>27.7511057650897</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>0.4720267441872952</v>
+        <v>0.5159660697903209</v>
       </c>
       <c r="K194" s="2" t="n">
         <v>0</v>
@@ -10746,11 +10746,11 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>0.0349936220506823</v>
+        <v>-0.3754997355572058</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
@@ -11604,21 +11604,21 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>2614</v>
+        <v>3025</v>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>東森</t>
+          <t>星通</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
         <v/>
       </c>
       <c r="D211" s="2" t="n">
-        <v>266.4582962253791</v>
+        <v>275.6895775045783</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>18.2</v>
+        <v>59.8</v>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
@@ -11629,16 +11629,16 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>42.0282853388065</v>
+        <v>31.73838667824074</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>13.89473530435108</v>
+        <v>20.97133487115907</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>0.4745403447478912</v>
+        <v>0.5471009982681534</v>
       </c>
       <c r="K211" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L211" s="2" t="n">
         <v>0</v>
@@ -11647,31 +11647,31 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>-0.0025094517054839</v>
+        <v>-1.150579877727757</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>3021</v>
+        <v>2614</v>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>鴻名</t>
+          <t>東森</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
         <v/>
       </c>
       <c r="D212" s="2" t="n">
-        <v>263.5707269617915</v>
+        <v>266.4582962253791</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>26.5</v>
+        <v>18.2</v>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
@@ -11682,16 +11682,16 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>44.77821132891011</v>
+        <v>42.0282853388065</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>19.52637285959432</v>
+        <v>13.89473530435108</v>
       </c>
       <c r="J212" s="2" t="n">
-        <v>0.5761921981121406</v>
+        <v>0.4745403447478912</v>
       </c>
       <c r="K212" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L212" s="2" t="n">
         <v>0</v>
@@ -11700,31 +11700,31 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>-0.670013366313128</v>
+        <v>-0.0025094517054839</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>3025</v>
+        <v>3021</v>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>星通</t>
+          <t>鴻名</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
         <v/>
       </c>
       <c r="D213" s="2" t="n">
-        <v>260.6895775045783</v>
+        <v>263.5707269617915</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>59.8</v>
+        <v>26.5</v>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
@@ -11735,13 +11735,13 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>31.73838667824074</v>
+        <v>44.77821132891011</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>20.97133487115907</v>
+        <v>19.52637285959432</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>0.5471009982681534</v>
+        <v>0.5761921981121406</v>
       </c>
       <c r="K213" s="2" t="n">
         <v>0</v>
@@ -11753,31 +11753,31 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>-1.150579877727757</v>
+        <v>-0.670013366313128</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>3044</v>
+        <v>2474</v>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
         <v/>
       </c>
       <c r="D214" s="2" t="n">
-        <v>257.6742730321028</v>
+        <v>258.5784955035905</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>448.5</v>
+        <v>195.5</v>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
@@ -11788,25 +11788,25 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>35.98613935747048</v>
+        <v>42.68352461575753</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>16.14283741421294</v>
+        <v>17.08423417219415</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>1.161102924884923</v>
+        <v>0.5029944905399072</v>
       </c>
       <c r="K214" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L214" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M214" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>-9.568763252189829</v>
+        <v>-1.386139219430503</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -11816,21 +11816,21 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>3010</v>
+        <v>3044</v>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>華立</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
         <v/>
       </c>
       <c r="D215" s="2" t="n">
-        <v>257.6261656830181</v>
+        <v>257.6742730321028</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>117.5</v>
+        <v>448.5</v>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
@@ -11841,13 +11841,13 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>32.83687192909305</v>
+        <v>35.98613935747048</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>15.3862653495066</v>
+        <v>16.14283741421294</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>1.271456762033636</v>
+        <v>1.161102924884923</v>
       </c>
       <c r="K215" s="2" t="n">
         <v>0</v>
@@ -11859,7 +11859,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.6309660580423424</v>
+        <v>-9.568763252189829</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11869,21 +11869,21 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>華立</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
         <v/>
       </c>
       <c r="D216" s="2" t="n">
-        <v>256.4113941534264</v>
+        <v>257.6261656830181</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>299</v>
+        <v>117.5</v>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
@@ -11894,13 +11894,13 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>38.87944165220431</v>
+        <v>32.83687192909305</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>19.11111313705961</v>
+        <v>15.3862653495066</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>0.4266909426463545</v>
+        <v>1.271456762033636</v>
       </c>
       <c r="K216" s="2" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>-2.384554233287997</v>
+        <v>-0.6309660580423424</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11922,21 +11922,21 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>2489</v>
+        <v>3030</v>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>瑞軒</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
         <v/>
       </c>
       <c r="D217" s="2" t="n">
-        <v>250.3554687871176</v>
+        <v>256.4113941534264</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>38.4</v>
+        <v>299</v>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
@@ -11947,13 +11947,13 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>36.99493804697372</v>
+        <v>38.87944165220431</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>17.82025781113965</v>
+        <v>19.11111313705961</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>0.283887984662483</v>
+        <v>0.4266909426463545</v>
       </c>
       <c r="K217" s="2" t="n">
         <v>0</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>-0.7458109301704614</v>
+        <v>-2.384554233287997</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -11975,21 +11975,21 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>2474</v>
+        <v>2489</v>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>瑞軒</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
         <v/>
       </c>
       <c r="D218" s="2" t="n">
-        <v>243.5784955035905</v>
+        <v>240.3554687871176</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>195.5</v>
+        <v>38.4</v>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
@@ -12000,25 +12000,25 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>42.68352461575753</v>
+        <v>36.99493804697372</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>17.08423417219415</v>
+        <v>17.82025781113965</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>0.5029944905399072</v>
+        <v>0.283887984662483</v>
       </c>
       <c r="K218" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L218" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M218" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>-1.386139219430503</v>
+        <v>-0.7458109301704614</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>

--- a/output/full_scan/batch_seq3_2026-07-09.xlsx
+++ b/output/full_scan/batch_seq3_2026-07-09.xlsx
@@ -7364,21 +7364,21 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>3018</v>
+        <v>3045</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>隆銘綠能</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>509.2031715851631</v>
+        <v>509.5105669229774</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>12.05</v>
+        <v>108.5</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>52.96042354178515</v>
+        <v>28.61825215344104</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>14.00411353344998</v>
+        <v>24.1905696067152</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>1.782279900691022</v>
+        <v>3.35105669229774</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.129868093056733</v>
+        <v>-1.125708078864336</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>2546</v>
+        <v>3018</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>根基</t>
+          <t>隆銘綠能</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>505.6918777352019</v>
+        <v>509.2031715851631</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>92.2</v>
+        <v>12.05</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,16 +7442,16 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>49.9323048554422</v>
+        <v>52.96042354178515</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>32.60395640960779</v>
+        <v>14.00411353344998</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.4950859361523834</v>
+        <v>1.782279900691022</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.469436052221289</v>
+        <v>0.129868093056733</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>2471</v>
+        <v>2546</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>資通</t>
+          <t>根基</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>503.012503951619</v>
+        <v>505.6918777352019</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>53.2</v>
+        <v>92.2</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,16 +7495,16 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>51.51269854591602</v>
+        <v>49.9323048554422</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>11.9493841565906</v>
+        <v>32.60395640960779</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.4179962674339422</v>
+        <v>0.4950859361523834</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="2" t="n">
         <v>0</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.0016340680262111</v>
+        <v>-0.469436052221289</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>2459</v>
+        <v>2471</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>敦吉</t>
+          <t>資通</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>501.0279350152362</v>
+        <v>503.012503951619</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>63.7</v>
+        <v>53.2</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,13 +7548,13 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>39.33170025812593</v>
+        <v>51.51269854591602</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>24.2600086006961</v>
+        <v>11.9493841565906</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.2725027174650308</v>
+        <v>0.4179962674339422</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>0</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-0.0429512561549253</v>
+        <v>-0.0016340680262111</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>3073</v>
+        <v>2459</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>天方能源</t>
+          <t>敦吉</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>499.2337368577561</v>
+        <v>501.0279350152362</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>22</v>
+        <v>63.7</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,13 +7601,13 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>50.7709844566271</v>
+        <v>39.33170025812593</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>20.47660706899832</v>
+        <v>24.2600086006961</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.6276859944218266</v>
+        <v>0.2725027174650308</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>0</v>
@@ -7619,31 +7619,31 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>0.0916149920180276</v>
+        <v>-0.0429512561549253</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>3041</v>
+        <v>3073</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>揚智</t>
+          <t>天方能源</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>498.4394930957397</v>
+        <v>499.2337368577561</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>26.45</v>
+        <v>22</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,13 +7654,13 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>46.79258800013102</v>
+        <v>50.7709844566271</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>21.62521832728444</v>
+        <v>20.47660706899832</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.272872747042126</v>
+        <v>0.6276859944218266</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>0</v>
@@ -7672,31 +7672,31 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>-0.3574170756442113</v>
+        <v>0.0916149920180276</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>3002</v>
+        <v>3041</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>歐格</t>
+          <t>揚智</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>497.2449589827172</v>
+        <v>498.4394930957397</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>20.45</v>
+        <v>26.45</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,13 +7707,13 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>48.96783905627235</v>
+        <v>46.79258800013102</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>35.60455543350986</v>
+        <v>21.62521832728444</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.2916001953823394</v>
+        <v>0.272872747042126</v>
       </c>
       <c r="K137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-0.1917893926327997</v>
+        <v>-0.3574170756442113</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>2731</v>
+        <v>3002</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>雄獅</t>
+          <t>歐格</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>496.6071263236449</v>
+        <v>497.2449589827172</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>145.5</v>
+        <v>20.45</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,13 +7760,13 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>30.88348934736115</v>
+        <v>48.96783905627235</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>23.33322271680851</v>
+        <v>35.60455543350986</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.9235818372441584</v>
+        <v>0.2916001953823394</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>0</v>
@@ -7778,31 +7778,31 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.0951940029337965</v>
+        <v>-0.1917893926327997</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>2608</v>
+        <v>2731</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>嘉里大榮</t>
+          <t>雄獅</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>495.8506033487794</v>
+        <v>496.6071263236449</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>29.45</v>
+        <v>145.5</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,16 +7813,16 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>54.13420944703902</v>
+        <v>30.88348934736115</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>19.4644188259638</v>
+        <v>23.33322271680851</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.5327558711538301</v>
+        <v>0.9235818372441584</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L139" s="2" t="n">
         <v>0</v>
@@ -7831,31 +7831,31 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>0.0715435705266575</v>
+        <v>-0.0951940029337965</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>2462</v>
+        <v>2608</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>良得電</t>
+          <t>嘉里大榮</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>490.0669938718079</v>
+        <v>495.8506033487794</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>22.85</v>
+        <v>29.45</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,16 +7866,16 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>42.00613390511628</v>
+        <v>54.13420944703902</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>17.98530594241905</v>
+        <v>19.4644188259638</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.3790319613823146</v>
+        <v>0.5327558711538301</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L140" s="2" t="n">
         <v>0</v>
@@ -7884,31 +7884,31 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.3037596928425445</v>
+        <v>0.0715435705266575</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>3045</v>
+        <v>2462</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>良得電</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>489.5105669229774</v>
+        <v>490.0669938718079</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>108.5</v>
+        <v>22.85</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,16 +7919,16 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>28.61825215344104</v>
+        <v>42.00613390511628</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>24.1905696067152</v>
+        <v>17.98530594241905</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>3.35105669229774</v>
+        <v>0.3790319613823146</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L141" s="2" t="n">
         <v>0</v>
@@ -7937,11 +7937,11 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>-1.125708078864336</v>
+        <v>-0.3037596928425445</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
